--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_LITHIUM IBERIA SAGRADO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_LITHIUM IBERIA SAGRADO.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>77.6901</v>
+        <v>94.5378</v>
       </c>
       <c r="E2" t="n">
-        <v>86.9798</v>
+        <v>96.94240000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-9.2897</v>
+        <v>-2.404600000000001</v>
       </c>
       <c r="G2" t="n">
         <v>61.1737</v>
@@ -610,13 +610,13 @@
         <v>56.8831</v>
       </c>
       <c r="S2" t="n">
-        <v>-23.2252</v>
+        <v>-6.377699999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-11.0942</v>
+        <v>-1.1315</v>
       </c>
       <c r="U2" t="n">
-        <v>-12.1308</v>
+        <v>-5.2458</v>
       </c>
       <c r="V2" t="n">
         <v>41.2236</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. CISSE</t>
+          <t>M. CASERO MIGLIAVACCA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>54.1041</v>
+        <v>59.696</v>
       </c>
       <c r="E3" t="n">
-        <v>64.9237</v>
+        <v>58.9585</v>
       </c>
       <c r="F3" t="n">
-        <v>-10.8195</v>
+        <v>0.7372000000000007</v>
       </c>
       <c r="G3" t="n">
-        <v>40.838</v>
+        <v>34.2681</v>
       </c>
       <c r="H3" t="n">
-        <v>22.1447</v>
+        <v>2.491099999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>18.6934</v>
+        <v>31.7769</v>
       </c>
       <c r="J3" t="n">
-        <v>75.3445</v>
+        <v>64.0188</v>
       </c>
       <c r="K3" t="n">
-        <v>49.7805</v>
+        <v>33.1128</v>
       </c>
       <c r="L3" t="n">
-        <v>25.5638</v>
+        <v>30.9058</v>
       </c>
       <c r="M3" t="n">
-        <v>-34.5065</v>
+        <v>-29.7504</v>
       </c>
       <c r="N3" t="n">
-        <v>-27.6359</v>
+        <v>-30.6216</v>
       </c>
       <c r="O3" t="n">
-        <v>-6.8706</v>
+        <v>0.8711000000000004</v>
       </c>
       <c r="P3" t="n">
-        <v>-10.1909</v>
+        <v>25.5696</v>
       </c>
       <c r="Q3" t="n">
-        <v>-59.6624</v>
+        <v>-23.5313</v>
       </c>
       <c r="R3" t="n">
-        <v>49.4715</v>
+        <v>49.1014</v>
       </c>
       <c r="S3" t="n">
-        <v>17.669</v>
+        <v>-4.7355</v>
       </c>
       <c r="T3" t="n">
-        <v>10.8543</v>
+        <v>-1.6637</v>
       </c>
       <c r="U3" t="n">
-        <v>6.8149</v>
+        <v>-3.0719</v>
       </c>
       <c r="V3" t="n">
-        <v>5.787700000000001</v>
+        <v>4.594</v>
       </c>
       <c r="W3" t="n">
-        <v>38.3876</v>
+        <v>20.135</v>
       </c>
       <c r="X3" t="n">
-        <v>-32.6</v>
+        <v>-15.5414</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. CASERO MIGLIAVACCA</t>
+          <t>S. CISSE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>50.7813</v>
+        <v>43.8293</v>
       </c>
       <c r="E4" t="n">
-        <v>53.0659</v>
+        <v>60.1536</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.284400000000001</v>
+        <v>-16.3242</v>
       </c>
       <c r="G4" t="n">
-        <v>34.2681</v>
+        <v>40.838</v>
       </c>
       <c r="H4" t="n">
-        <v>2.491099999999999</v>
+        <v>22.1447</v>
       </c>
       <c r="I4" t="n">
-        <v>31.7769</v>
+        <v>18.6934</v>
       </c>
       <c r="J4" t="n">
-        <v>64.0188</v>
+        <v>75.3445</v>
       </c>
       <c r="K4" t="n">
-        <v>33.1128</v>
+        <v>49.7805</v>
       </c>
       <c r="L4" t="n">
-        <v>30.9058</v>
+        <v>25.5638</v>
       </c>
       <c r="M4" t="n">
-        <v>-29.7504</v>
+        <v>-34.5065</v>
       </c>
       <c r="N4" t="n">
-        <v>-30.6216</v>
+        <v>-27.6359</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8711000000000004</v>
+        <v>-6.8706</v>
       </c>
       <c r="P4" t="n">
-        <v>25.5696</v>
+        <v>-10.1909</v>
       </c>
       <c r="Q4" t="n">
-        <v>-23.5313</v>
+        <v>-59.6624</v>
       </c>
       <c r="R4" t="n">
-        <v>49.1014</v>
+        <v>49.4715</v>
       </c>
       <c r="S4" t="n">
-        <v>-13.6502</v>
+        <v>7.3944</v>
       </c>
       <c r="T4" t="n">
-        <v>-7.5563</v>
+        <v>6.0841</v>
       </c>
       <c r="U4" t="n">
-        <v>-6.0937</v>
+        <v>1.3102</v>
       </c>
       <c r="V4" t="n">
-        <v>4.594</v>
+        <v>5.787700000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>20.135</v>
+        <v>38.3876</v>
       </c>
       <c r="X4" t="n">
-        <v>-15.5414</v>
+        <v>-32.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. RAMOS CASTRO</t>
+          <t>B. LEÓN TEJERA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>30.2224</v>
+        <v>26.6918</v>
       </c>
       <c r="E5" t="n">
-        <v>26.257</v>
+        <v>26.6918</v>
       </c>
       <c r="F5" t="n">
-        <v>3.9652</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>16.3525</v>
+        <v>26.6918</v>
       </c>
       <c r="H5" t="n">
-        <v>25.0169</v>
+        <v>7.4077</v>
       </c>
       <c r="I5" t="n">
-        <v>-8.6645</v>
+        <v>19.2843</v>
       </c>
       <c r="J5" t="n">
-        <v>40.1077</v>
+        <v>26.6918</v>
       </c>
       <c r="K5" t="n">
-        <v>45.2802</v>
+        <v>7.4077</v>
       </c>
       <c r="L5" t="n">
-        <v>-5.172800000000001</v>
+        <v>19.2843</v>
       </c>
       <c r="M5" t="n">
-        <v>-23.7552</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-20.2632</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.492</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-11.3025</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-45.3951</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>34.0929</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>19.4497</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>14.2453</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>5.2048</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>5.722300000000001</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>17.2996</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-11.5772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. LEÓN TEJERA</t>
+          <t>L. RAMOS CASTRO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>26.6918</v>
+        <v>16.3824</v>
       </c>
       <c r="E6" t="n">
-        <v>26.6918</v>
+        <v>16.467</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-0.0848000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>26.6918</v>
+        <v>16.3525</v>
       </c>
       <c r="H6" t="n">
-        <v>7.4077</v>
+        <v>25.0169</v>
       </c>
       <c r="I6" t="n">
-        <v>19.2843</v>
+        <v>-8.6645</v>
       </c>
       <c r="J6" t="n">
-        <v>26.6918</v>
+        <v>40.1077</v>
       </c>
       <c r="K6" t="n">
-        <v>7.4077</v>
+        <v>45.2802</v>
       </c>
       <c r="L6" t="n">
-        <v>19.2843</v>
+        <v>-5.172800000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-23.7552</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-20.2632</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-3.492</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-11.3025</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-45.3951</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>34.0929</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>4.4552</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.1548</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>5.722300000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>17.2996</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-11.5772</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. KALLE</t>
+          <t>B. LEON TEJERA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D7" t="n">
-        <v>21.0945</v>
+        <v>12.4029</v>
       </c>
       <c r="E7" t="n">
-        <v>15.6873</v>
+        <v>4.6266</v>
       </c>
       <c r="F7" t="n">
-        <v>5.407500000000001</v>
+        <v>7.7766</v>
       </c>
       <c r="G7" t="n">
-        <v>8.6592</v>
+        <v>-9.365399999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>2.984</v>
+        <v>-11.9195</v>
       </c>
       <c r="I7" t="n">
-        <v>5.6748</v>
+        <v>2.554</v>
       </c>
       <c r="J7" t="n">
-        <v>24.6708</v>
+        <v>6.817499999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>18.315</v>
+        <v>4.3888</v>
       </c>
       <c r="L7" t="n">
-        <v>6.3557</v>
+        <v>2.4285</v>
       </c>
       <c r="M7" t="n">
-        <v>-16.0118</v>
+        <v>-16.1829</v>
       </c>
       <c r="N7" t="n">
-        <v>-15.3307</v>
+        <v>-16.3086</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6808999999999998</v>
+        <v>0.1254000000000003</v>
       </c>
       <c r="P7" t="n">
-        <v>10.932</v>
+        <v>10.5612</v>
       </c>
       <c r="Q7" t="n">
-        <v>-20.0108</v>
+        <v>-29.09</v>
       </c>
       <c r="R7" t="n">
-        <v>30.943</v>
+        <v>39.6514</v>
       </c>
       <c r="S7" t="n">
-        <v>17.048</v>
+        <v>-2.6384</v>
       </c>
       <c r="T7" t="n">
-        <v>11.6624</v>
+        <v>0.1548</v>
       </c>
       <c r="U7" t="n">
-        <v>5.3859</v>
+        <v>-2.7933</v>
       </c>
       <c r="V7" t="n">
-        <v>-15.5445</v>
+        <v>13.8456</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.6351000000000001</v>
+        <v>26.7442</v>
       </c>
       <c r="X7" t="n">
-        <v>-14.9095</v>
+        <v>-12.8986</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. PARRA RIVERA</t>
+          <t>S. KALLE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2576</v>
+        <v>10.869</v>
       </c>
       <c r="E8" t="n">
-        <v>3.4709</v>
+        <v>8.8146</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.2136</v>
+        <v>2.0545</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3669</v>
+        <v>8.6592</v>
       </c>
       <c r="H8" t="n">
-        <v>5.824699999999997</v>
+        <v>2.984</v>
       </c>
       <c r="I8" t="n">
-        <v>-7.1914</v>
+        <v>5.6748</v>
       </c>
       <c r="J8" t="n">
-        <v>29.8694</v>
+        <v>24.6708</v>
       </c>
       <c r="K8" t="n">
-        <v>32.2566</v>
+        <v>18.315</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.3872</v>
+        <v>6.3557</v>
       </c>
       <c r="M8" t="n">
-        <v>-31.2364</v>
+        <v>-16.0118</v>
       </c>
       <c r="N8" t="n">
-        <v>-26.4317</v>
+        <v>-15.3307</v>
       </c>
       <c r="O8" t="n">
-        <v>-4.8041</v>
+        <v>-0.6808999999999998</v>
       </c>
       <c r="P8" t="n">
-        <v>10.0055</v>
+        <v>10.932</v>
       </c>
       <c r="Q8" t="n">
-        <v>-37.7984</v>
+        <v>-20.0108</v>
       </c>
       <c r="R8" t="n">
-        <v>47.80399999999999</v>
+        <v>30.943</v>
       </c>
       <c r="S8" t="n">
-        <v>13.2615</v>
+        <v>6.8228</v>
       </c>
       <c r="T8" t="n">
-        <v>7.6285</v>
+        <v>4.79</v>
       </c>
       <c r="U8" t="n">
-        <v>5.6332</v>
+        <v>2.0329</v>
       </c>
       <c r="V8" t="n">
-        <v>-20.6431</v>
+        <v>-15.5445</v>
       </c>
       <c r="W8" t="n">
-        <v>3.7717</v>
+        <v>-0.6351000000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>-24.4147</v>
+        <v>-14.9095</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. SÁNCHEZ RENA</t>
+          <t>J. SANCHEZ BARQUIN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6221</v>
+        <v>8.887700000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6221</v>
+        <v>22.1762</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>-13.2885</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6221</v>
+        <v>30.5651</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.1139000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6221</v>
+        <v>30.4514</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6221</v>
+        <v>68.11070000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>30.9969</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6221</v>
+        <v>37.1143</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-37.5455</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-30.8827</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-6.6628</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-8.3378</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-54.4742</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>46.1363</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-7.6179</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-1.8447</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-5.773</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-5.7219</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>10.3848</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-16.1064</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. CASAS GARCÍA</t>
+          <t>J. SÁNCHEZ RENA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,31 +1189,31 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3221</v>
+        <v>0.6221</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3221</v>
+        <v>0.6221</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3221</v>
+        <v>0.6221</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3221</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.6221</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3221</v>
+        <v>0.6221</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3221</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.6221</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1597</v>
+        <v>0.3376</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4901</v>
+        <v>0.5448</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3303</v>
+        <v>-0.2072</v>
       </c>
       <c r="G11" t="n">
         <v>0.1871</v>
@@ -1312,13 +1312,13 @@
         <v>0.1853</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2126</v>
+        <v>-0.0348</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1641</v>
+        <v>-0.1094</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0485</v>
+        <v>0.0746</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. SANCHEZ RENA</t>
+          <t>S. CASAS GARCÍA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.0703</v>
+        <v>0.3221</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9577</v>
+        <v>0.3221</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0281</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.9154</v>
+        <v>0.3221</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.05220000000000001</v>
+        <v>0.3221</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.8632</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1702999999999999</v>
+        <v>0.3221</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1074</v>
+        <v>0.3221</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06279999999999997</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.0856</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1596</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.926</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0.7412</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7412</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.785</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4714</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3136</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.8888</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. DOMINGOS CUADRADO</t>
+          <t>J. SANCHEZ RENA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.0238</v>
+        <v>-0.6779999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.0637</v>
+        <v>1.2514</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9601</v>
+        <v>-1.9295</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.4826</v>
+        <v>-2.9154</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2629</v>
+        <v>-0.05220000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2196</v>
+        <v>-2.8632</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.9207000000000001</v>
+        <v>0.1702999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.3094</v>
+        <v>0.1074</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.6114000000000001</v>
+        <v>0.06279999999999997</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4381</v>
+        <v>-3.0856</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0464</v>
+        <v>-0.1596</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3917</v>
+        <v>-2.926</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1853</v>
+        <v>0.7412</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.1853</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.3706</v>
+        <v>0.7412</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1532</v>
+        <v>-0.3926</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0423</v>
+        <v>-0.1775</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1955</v>
+        <v>-0.2151</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.5733</v>
+        <v>1.8888</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.5733</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. GALIANO AVILA</t>
+          <t>P. DOMINGOS CUADRADO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.472</v>
+        <v>-1.7726</v>
       </c>
       <c r="E14" t="n">
-        <v>1.614099999999999</v>
+        <v>-0.9111</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.086</v>
+        <v>-0.8614999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.683199999999999</v>
+        <v>-0.4826</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.2964</v>
+        <v>-0.2629</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.3868</v>
+        <v>-0.2196</v>
       </c>
       <c r="J14" t="n">
-        <v>11.9684</v>
+        <v>-0.9207000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>11.5924</v>
+        <v>-0.3094</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3756999999999997</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-16.6516</v>
+        <v>0.4381</v>
       </c>
       <c r="N14" t="n">
-        <v>-13.8889</v>
+        <v>0.0464</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.7627</v>
+        <v>0.3917</v>
       </c>
       <c r="P14" t="n">
-        <v>13.8965</v>
+        <v>0.1853</v>
       </c>
       <c r="Q14" t="n">
-        <v>-15.0082</v>
+        <v>-0.1853</v>
       </c>
       <c r="R14" t="n">
-        <v>28.9047</v>
+        <v>0.3706</v>
       </c>
       <c r="S14" t="n">
-        <v>4.863</v>
+        <v>0.0979</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8257</v>
+        <v>0.195</v>
       </c>
       <c r="U14" t="n">
-        <v>3.0375</v>
+        <v>-0.097</v>
       </c>
       <c r="V14" t="n">
-        <v>-16.5483</v>
+        <v>-1.5733</v>
       </c>
       <c r="W14" t="n">
-        <v>2.8283</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-19.3767</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. LEON TEJERA</t>
+          <t>J. CACHO REGUERO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.1552</v>
+        <v>-2.3546</v>
       </c>
       <c r="E15" t="n">
-        <v>-4.8696</v>
+        <v>-1.2785</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7142</v>
+        <v>-1.0761</v>
       </c>
       <c r="G15" t="n">
-        <v>-9.365399999999999</v>
+        <v>-2.5792</v>
       </c>
       <c r="H15" t="n">
-        <v>-11.9195</v>
+        <v>-0.5316</v>
       </c>
       <c r="I15" t="n">
-        <v>2.554</v>
+        <v>-2.0476</v>
       </c>
       <c r="J15" t="n">
-        <v>6.817499999999999</v>
+        <v>-0.9608</v>
       </c>
       <c r="K15" t="n">
-        <v>4.3888</v>
+        <v>0.365</v>
       </c>
       <c r="L15" t="n">
-        <v>2.4285</v>
+        <v>-1.3259</v>
       </c>
       <c r="M15" t="n">
-        <v>-16.1829</v>
+        <v>-1.6184</v>
       </c>
       <c r="N15" t="n">
-        <v>-16.3086</v>
+        <v>-0.8965000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1254000000000003</v>
+        <v>-0.7219</v>
       </c>
       <c r="P15" t="n">
-        <v>10.5612</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q15" t="n">
-        <v>-29.09</v>
+        <v>-0.9264</v>
       </c>
       <c r="R15" t="n">
-        <v>39.6514</v>
+        <v>0.7411</v>
       </c>
       <c r="S15" t="n">
-        <v>-18.1966</v>
+        <v>0.7244</v>
       </c>
       <c r="T15" t="n">
-        <v>-9.3408</v>
+        <v>0.6087</v>
       </c>
       <c r="U15" t="n">
-        <v>-8.855499999999999</v>
+        <v>0.1157</v>
       </c>
       <c r="V15" t="n">
-        <v>13.8456</v>
+        <v>-0.3144</v>
       </c>
       <c r="W15" t="n">
-        <v>26.7442</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-12.8986</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. CASAS GARCIA</t>
+          <t>S. KVERNADZE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>-3.1743</v>
+        <v>-2.385799999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5996999999999999</v>
+        <v>-4.42</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.7739</v>
+        <v>2.0342</v>
       </c>
       <c r="G16" t="n">
-        <v>-4.8622</v>
+        <v>-6.180299999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.1834</v>
+        <v>-2.524500000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.6785</v>
+        <v>-3.656199999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3409</v>
+        <v>7.176900000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3229000000000002</v>
+        <v>10.8276</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6635</v>
+        <v>-3.6509</v>
       </c>
       <c r="M16" t="n">
-        <v>-5.202900000000001</v>
+        <v>-13.357</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.8609</v>
+        <v>-13.3519</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.3421</v>
+        <v>-0.00479999999999977</v>
       </c>
       <c r="P16" t="n">
-        <v>2.4088</v>
+        <v>15.5641</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.7793</v>
+        <v>-16.8609</v>
       </c>
       <c r="R16" t="n">
-        <v>5.188099999999999</v>
+        <v>32.4251</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9133999999999999</v>
+        <v>-2.5822</v>
       </c>
       <c r="T16" t="n">
-        <v>2.0955</v>
+        <v>2.1201</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.1817</v>
+        <v>-4.7022</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.6344</v>
+        <v>-9.1876</v>
       </c>
       <c r="W16" t="n">
-        <v>0.9427</v>
+        <v>3.1443</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.5771</v>
+        <v>-12.332</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. CACHO REGUERO</t>
+          <t>S. CASAS GARCIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.254</v>
+        <v>-4.1694</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.0302</v>
+        <v>-0.8463000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2238</v>
+        <v>-3.3232</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.5792</v>
+        <v>-4.8622</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5316</v>
+        <v>-3.1834</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.0476</v>
+        <v>-1.6785</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9608</v>
+        <v>0.3409</v>
       </c>
       <c r="K17" t="n">
-        <v>0.365</v>
+        <v>-0.3229000000000002</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.3259</v>
+        <v>0.6635</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6184</v>
+        <v>-5.202900000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8965000000000001</v>
+        <v>-2.8609</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7219</v>
+        <v>-2.3421</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1853</v>
+        <v>2.4088</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9264</v>
+        <v>-2.7793</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7411</v>
+        <v>5.188099999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1751</v>
+        <v>-0.08170000000000009</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.143</v>
+        <v>0.6495</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.03209999999999999</v>
+        <v>-0.7313</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3144</v>
+        <v>-1.6344</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.9427</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3144</v>
+        <v>-2.5771</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. SANCHEZ BARQUIN</t>
+          <t>H. SANTOS PARRA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>-5.216399999999998</v>
+        <v>-4.5971</v>
       </c>
       <c r="E18" t="n">
-        <v>14.3593</v>
+        <v>-4.2597</v>
       </c>
       <c r="F18" t="n">
-        <v>-19.5754</v>
+        <v>-0.3375000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>30.5651</v>
+        <v>-8.479199999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1139000000000001</v>
+        <v>-3.8003</v>
       </c>
       <c r="I18" t="n">
-        <v>30.4514</v>
+        <v>-4.6788</v>
       </c>
       <c r="J18" t="n">
-        <v>68.11070000000001</v>
+        <v>-4.4823</v>
       </c>
       <c r="K18" t="n">
-        <v>30.9969</v>
+        <v>0.4500999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>37.1143</v>
+        <v>-4.932700000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>-37.5455</v>
+        <v>-3.9969</v>
       </c>
       <c r="N18" t="n">
-        <v>-30.8827</v>
+        <v>-4.2506</v>
       </c>
       <c r="O18" t="n">
-        <v>-6.6628</v>
+        <v>0.2537</v>
       </c>
       <c r="P18" t="n">
-        <v>-8.3378</v>
+        <v>5.3732</v>
       </c>
       <c r="Q18" t="n">
-        <v>-54.4742</v>
+        <v>-0.9264</v>
       </c>
       <c r="R18" t="n">
-        <v>46.1363</v>
+        <v>6.2997</v>
       </c>
       <c r="S18" t="n">
-        <v>-21.7214</v>
+        <v>0.7109000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>-9.6616</v>
+        <v>0.5207999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-12.0597</v>
+        <v>0.1902</v>
       </c>
       <c r="V18" t="n">
-        <v>-5.7219</v>
+        <v>-2.2023</v>
       </c>
       <c r="W18" t="n">
-        <v>10.3848</v>
+        <v>0.6283000000000001</v>
       </c>
       <c r="X18" t="n">
-        <v>-16.1064</v>
+        <v>-2.8305</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>H. SANTOS PARRA</t>
+          <t>S. GALIANO AVILA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D19" t="n">
-        <v>-6.7118</v>
+        <v>-4.6265</v>
       </c>
       <c r="E19" t="n">
-        <v>-5.2416</v>
+        <v>0.3234000000000004</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4701</v>
+        <v>-4.95</v>
       </c>
       <c r="G19" t="n">
-        <v>-8.479199999999999</v>
+        <v>-4.683199999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.8003</v>
+        <v>-2.2964</v>
       </c>
       <c r="I19" t="n">
-        <v>-4.6788</v>
+        <v>-2.3868</v>
       </c>
       <c r="J19" t="n">
-        <v>-4.4823</v>
+        <v>11.9684</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4500999999999999</v>
+        <v>11.5924</v>
       </c>
       <c r="L19" t="n">
-        <v>-4.932700000000001</v>
+        <v>0.3756999999999997</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.9969</v>
+        <v>-16.6516</v>
       </c>
       <c r="N19" t="n">
-        <v>-4.2506</v>
+        <v>-13.8889</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2537</v>
+        <v>-2.7627</v>
       </c>
       <c r="P19" t="n">
-        <v>5.3732</v>
+        <v>13.8965</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9264</v>
+        <v>-15.0082</v>
       </c>
       <c r="R19" t="n">
-        <v>6.2997</v>
+        <v>28.9047</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4038</v>
+        <v>2.7087</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4611999999999999</v>
+        <v>0.5355000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9423999999999999</v>
+        <v>2.1733</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.2023</v>
+        <v>-16.5483</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6283000000000001</v>
+        <v>2.8283</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.8305</v>
+        <v>-19.3767</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. KVERNADZE</t>
+          <t>A. PARRA RIVERA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,70 +1966,70 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D20" t="n">
-        <v>-10.2051</v>
+        <v>-7.5953</v>
       </c>
       <c r="E20" t="n">
-        <v>-8.789099999999999</v>
+        <v>-1.1893</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4158</v>
+        <v>-6.405799999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>-6.180299999999999</v>
+        <v>-1.3669</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.524500000000001</v>
+        <v>5.824699999999997</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.656199999999999</v>
+        <v>-7.1914</v>
       </c>
       <c r="J20" t="n">
-        <v>7.176900000000001</v>
+        <v>29.8694</v>
       </c>
       <c r="K20" t="n">
-        <v>10.8276</v>
+        <v>32.2566</v>
       </c>
       <c r="L20" t="n">
-        <v>-3.6509</v>
+        <v>-2.3872</v>
       </c>
       <c r="M20" t="n">
-        <v>-13.357</v>
+        <v>-31.2364</v>
       </c>
       <c r="N20" t="n">
-        <v>-13.3519</v>
+        <v>-26.4317</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.00479999999999977</v>
+        <v>-4.8041</v>
       </c>
       <c r="P20" t="n">
-        <v>15.5641</v>
+        <v>10.0055</v>
       </c>
       <c r="Q20" t="n">
-        <v>-16.8609</v>
+        <v>-37.7984</v>
       </c>
       <c r="R20" t="n">
-        <v>32.4251</v>
+        <v>47.80399999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>-10.4014</v>
+        <v>4.4086</v>
       </c>
       <c r="T20" t="n">
-        <v>-2.2492</v>
+        <v>2.9681</v>
       </c>
       <c r="U20" t="n">
-        <v>-8.1523</v>
+        <v>1.4408</v>
       </c>
       <c r="V20" t="n">
-        <v>-9.1876</v>
+        <v>-20.6431</v>
       </c>
       <c r="W20" t="n">
-        <v>3.1443</v>
+        <v>3.7717</v>
       </c>
       <c r="X20" t="n">
-        <v>-12.332</v>
+        <v>-24.4147</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>225.6628</v>
+        <v>246.3994</v>
       </c>
       <c r="E21" t="n">
-        <v>274.0473</v>
+        <v>284.9895999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-48.3838</v>
+        <v>-38.5904</v>
       </c>
       <c r="G21" t="n">
         <v>178.7653</v>
@@ -2089,19 +2089,19 @@
         <v>-365.0138</v>
       </c>
       <c r="R21" t="n">
-        <v>428.9394</v>
+        <v>428.9393999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>-16.7199</v>
+        <v>4.016900000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>7.212199999999999</v>
+        <v>18.155</v>
       </c>
       <c r="U21" t="n">
-        <v>-23.9295</v>
+        <v>-14.1371</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3077999999999967</v>
+        <v>-0.3078000000000003</v>
       </c>
       <c r="W21" t="n">
         <v>182.7909</v>
